--- a/doc/DevSecOps_Project_Tracker.xlsx
+++ b/doc/DevSecOps_Project_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haris\Desktop\Workspace\Devsecops-eks-3tire\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C116E51-1CEA-42D2-8B65-C431099D695D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AE9927-1F5F-44D8-8298-41A58D5EA485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
   <si>
     <t>Task</t>
   </si>
@@ -696,6 +696,9 @@
       <c r="B11" t="s">
         <v>21</v>
       </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -704,6 +707,9 @@
       <c r="B12" t="s">
         <v>22</v>
       </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -712,6 +718,9 @@
       <c r="B13" t="s">
         <v>23</v>
       </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -720,6 +729,9 @@
       <c r="B14" t="s">
         <v>24</v>
       </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -728,6 +740,9 @@
       <c r="B15" t="s">
         <v>25</v>
       </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -736,6 +751,9 @@
       <c r="B16" t="s">
         <v>26</v>
       </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -744,6 +762,9 @@
       <c r="B17" t="s">
         <v>27</v>
       </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -752,6 +773,9 @@
       <c r="B18" t="s">
         <v>28</v>
       </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -760,6 +784,9 @@
       <c r="B19" t="s">
         <v>29</v>
       </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -781,6 +808,9 @@
       </c>
       <c r="B21" t="s">
         <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -842,7 +872,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Tracker!C2:C100,"Not Started")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -851,7 +881,7 @@
       </c>
       <c r="B5">
         <f>COUNTIF(Tracker!C2:C100,"Completed")/COUNTIF(Tracker!C2:C100,"&lt;&gt;")</f>
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
